--- a/语文群_20261029.xlsx
+++ b/语文群_20261029.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qingg\Python\checkin\WeChatTextExport\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_FE6A51EB7C96931C4D34370D7992463DEF58E6DD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_FE6A51EB7C96931C4D34371CC15278DBEF58E6DD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
